--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4755-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4755-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A9B4C1D-4E59-454D-857E-4E0C9A58AC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FD243A3-ED18-40BA-B25D-D3A97D756B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{250C01B9-9C4E-46DF-BE5D-F1D846A03F07}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{784D60E8-B908-474F-8AAF-524A47E0B6A4}"/>
   </bookViews>
   <sheets>
     <sheet name="4755-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1499,30 +1499,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57F32B0-1375-47E9-BB79-BA6251B6E0DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D9F4AA-545B-4BD5-9EC4-CC1E14CFB62C}">
   <dimension ref="A1:X57"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1592,7 +1592,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1712,7 +1712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2023</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>29</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>29</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2021</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>29</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>29</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2020</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>29</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>29</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>29</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>29</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>29</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>29</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2019</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>29</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>29</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>29</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>2018</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>2017</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>2016</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>2015</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>2014</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="35">
         <v>2013</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="37">
         <v>2012</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>54</v>
       </c>
